--- a/samples/단골고객_샘플.xlsx
+++ b/samples/단골고객_샘플.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>지역</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>서울특별시 강남구 테헤란로 123 4층 401호</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>인천광역시 연수구 송도과학로 32 송도테크노파크 IT센터 12층</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>대구광역시 수성구 달구벌대로 2450</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>서울특별시 마포구 월드컵북로 400</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>부산광역시 수영구 광안해변로 219</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
